--- a/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,38</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,6</t>
+          <t>1,31; 7,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,39</t>
+          <t>0,46; 4,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 13,4</t>
+          <t>3,01; 14,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,96</t>
+          <t>0,77; 7,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,11</t>
+          <t>0,8; 7,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,02</t>
+          <t>0,63; 6,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,86</t>
+          <t>1,15; 4,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,75</t>
+          <t>0,66; 3,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,56</t>
+          <t>0,98; 4,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,57</t>
+          <t>1,97; 7,56</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,12</t>
+          <t>0,67; 4,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,23</t>
+          <t>0,88; 5,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,93</t>
+          <t>0,82; 4,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,04</t>
+          <t>3,44; 9,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,3</t>
+          <t>1,01; 4,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,39</t>
+          <t>0,35; 3,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,92</t>
+          <t>2,79; 7,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,18</t>
+          <t>3,5; 9,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,28</t>
+          <t>1,06; 3,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,49</t>
+          <t>0,83; 3,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,88</t>
+          <t>2,49; 5,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,97</t>
+          <t>4,12; 8,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,72</t>
+          <t>1,41; 8,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 8,66</t>
+          <t>1,6; 9,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,87</t>
+          <t>2,99; 9,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,98</t>
+          <t>4,19; 11,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,25</t>
+          <t>1,55; 7,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 9,83</t>
+          <t>3,12; 10,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,34</t>
+          <t>2,28; 7,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,9</t>
+          <t>1,99; 6,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,45</t>
+          <t>1,09; 5,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,51</t>
+          <t>3,93; 8,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,56</t>
+          <t>3,69; 7,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,58</t>
+          <t>0,8; 4,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,75</t>
+          <t>0,64; 6,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 15,21</t>
+          <t>6,02; 15,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,62</t>
+          <t>2,16; 6,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,31</t>
+          <t>1,06; 5,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,52</t>
+          <t>0,87; 5,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,76</t>
+          <t>2,2; 8,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,81</t>
+          <t>5,14; 10,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,06</t>
+          <t>1,24; 4,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,37</t>
+          <t>1,08; 4,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,22</t>
+          <t>4,8; 10,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,93</t>
+          <t>4,11; 7,81</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,38</t>
+          <t>1,35; 3,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,54</t>
+          <t>1,89; 4,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,75</t>
+          <t>3,57; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,06</t>
+          <t>4,05; 7,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,11</t>
+          <t>1,7; 4,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,39</t>
+          <t>0,75; 2,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,42</t>
+          <t>3,42; 6,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,53</t>
+          <t>4,34; 7,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,31</t>
+          <t>1,74; 3,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,05</t>
+          <t>1,44; 2,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,05</t>
+          <t>3,9; 6,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,74</t>
+          <t>4,58; 6,69</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3880</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2869</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3971</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4319</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1364; 7569</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>477; 4995</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1731; 8187</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>683; 6676</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>790; 7181</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>388; 3848</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1922; 8328</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1424; 7947</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1971; 9311</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2339; 8991</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3631</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3783</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9320</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10415</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10512</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7253</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6282</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14198</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>19832</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1258; 7868</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1398; 8027</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1285; 7552</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5476; 14913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1906; 8115</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>675; 6621</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5870; 16499</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6382; 16560</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3975; 12418</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2909; 11244</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9129; 21980</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>14067; 28887</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3344</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8577</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12098</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8017</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9070</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5684</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>16593</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>21168</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1219; 7708</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1565; 8919</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4318; 13415</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7287; 19353</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1598; 7884</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4514</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4129; 13401</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4839; 15685</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3767; 12472</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2181; 10361</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10866; 24029</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14269; 30110</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12190</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10763</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22951</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6082</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17977</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>33714</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1210; 6891</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>743; 7152</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7347; 18487</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5947; 17369</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1576; 8196</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1145; 7522</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2863; 11191</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>15693; 33068</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3705; 12403</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2677; 10811</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12092; 25697</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>23895; 45356</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26289</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36062</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>21585</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>53375</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>79916</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6795; 17334</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9022; 21847</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18735; 35273</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26948; 46707</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8985; 21348</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4017; 13079</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19518; 36715</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>33070; 55711</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>17985; 34398</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14645; 30019</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>42709; 65880</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>65472; 95484</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,27</t>
+          <t>1,28; 7,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,86</t>
+          <t>0,46; 4,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 14,23</t>
+          <t>2,92; 14,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,55</t>
+          <t>0,78; 6,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,31</t>
+          <t>0,8; 7,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,26</t>
+          <t>0,63; 6,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,99</t>
+          <t>0,79; 4,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,68</t>
+          <t>0,62; 3,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,63</t>
+          <t>0,96; 4,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,56</t>
+          <t>2,18; 7,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,2</t>
+          <t>0,67; 3,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,04</t>
+          <t>0,83; 5,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,83</t>
+          <t>0,83; 4,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,36</t>
+          <t>3,39; 9,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,3</t>
+          <t>0,72; 4,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,43</t>
+          <t>0,35; 3,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,83</t>
+          <t>2,85; 7,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,07</t>
+          <t>3,47; 9,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,3</t>
+          <t>1,03; 3,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,19</t>
+          <t>0,93; 3,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,99</t>
+          <t>2,36; 5,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 8,45</t>
+          <t>4,03; 8,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,91</t>
+          <t>1,41; 8,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,1</t>
+          <t>1,91; 8,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,3</t>
+          <t>3,12; 9,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 11,13</t>
+          <t>3,98; 10,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,64</t>
+          <t>1,56; 7,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 10,14</t>
+          <t>3,25; 10,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,38</t>
+          <t>2,22; 7,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,57</t>
+          <t>1,8; 6,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,19</t>
+          <t>1,36; 5,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,69</t>
+          <t>3,82; 8,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,79</t>
+          <t>3,62; 7,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,56</t>
+          <t>0,8; 4,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,19</t>
+          <t>0,64; 5,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 15,14</t>
+          <t>6,55; 15,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,31</t>
+          <t>2,22; 6,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,53</t>
+          <t>0,87; 5,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,71</t>
+          <t>0,9; 6,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,61</t>
+          <t>2,18; 8,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,82</t>
+          <t>5,02; 10,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,15</t>
+          <t>1,26; 3,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,37</t>
+          <t>1,15; 4,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,19</t>
+          <t>4,81; 10,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,81</t>
+          <t>4,19; 7,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,44</t>
+          <t>1,25; 3,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,58</t>
+          <t>1,84; 4,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,71</t>
+          <t>3,72; 6,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,01</t>
+          <t>4,17; 7,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,04</t>
+          <t>1,74; 3,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,43</t>
+          <t>0,73; 2,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,43</t>
+          <t>3,5; 6,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,31</t>
+          <t>4,41; 7,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,33</t>
+          <t>1,76; 3,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,96</t>
+          <t>1,43; 2,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,01</t>
+          <t>3,79; 5,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,69</t>
+          <t>4,58; 6,72</t>
         </is>
       </c>
     </row>
@@ -1645,27 +1645,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4319</t>
+          <t>0; 3877</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1364; 7569</t>
+          <t>1335; 8248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>477; 4995</t>
+          <t>476; 4789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1731; 8187</t>
+          <t>1679; 8060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>683; 6676</t>
+          <t>688; 6164</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1675,32 +1675,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>790; 7181</t>
+          <t>786; 7300</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>388; 3848</t>
+          <t>387; 3940</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1922; 8328</t>
+          <t>1328; 8078</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1424; 7947</t>
+          <t>1338; 7819</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1971; 9311</t>
+          <t>1920; 8937</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2339; 8991</t>
+          <t>2598; 9023</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1258; 7868</t>
+          <t>1248; 7351</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1398; 8027</t>
+          <t>1323; 8074</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1285; 7552</t>
+          <t>1289; 7725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5476; 14913</t>
+          <t>5402; 14740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1906; 8115</t>
+          <t>1350; 8237</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>675; 6621</t>
+          <t>680; 6540</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5870; 16499</t>
+          <t>6007; 16192</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6382; 16560</t>
+          <t>6333; 16945</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3975; 12418</t>
+          <t>3867; 12327</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2909; 11244</t>
+          <t>3267; 12360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9129; 21980</t>
+          <t>8653; 21749</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14067; 28887</t>
+          <t>13765; 27993</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1219; 7708</t>
+          <t>1220; 7754</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1565; 8919</t>
+          <t>1868; 8539</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4318; 13415</t>
+          <t>4504; 13604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7287; 19353</t>
+          <t>6922; 18866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1598; 7884</t>
+          <t>1606; 8001</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 5069</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4129; 13401</t>
+          <t>4299; 13610</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4839; 15685</t>
+          <t>4714; 15849</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3767; 12472</t>
+          <t>3412; 12044</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2181; 10361</t>
+          <t>2708; 11292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10866; 24029</t>
+          <t>10573; 23456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14269; 30110</t>
+          <t>13989; 30376</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1210; 6891</t>
+          <t>1202; 6381</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>743; 7152</t>
+          <t>734; 6884</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7347; 18487</t>
+          <t>8001; 18744</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5947; 17369</t>
+          <t>6117; 17633</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1576; 8196</t>
+          <t>1283; 7587</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1145; 7522</t>
+          <t>1179; 7939</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2863; 11191</t>
+          <t>2838; 11015</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15693; 33068</t>
+          <t>15345; 32955</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3705; 12403</t>
+          <t>3777; 11797</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2677; 10811</t>
+          <t>2853; 11266</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12092; 25697</t>
+          <t>12134; 26401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23895; 45356</t>
+          <t>24337; 45429</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6795; 17334</t>
+          <t>6303; 17237</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9022; 21847</t>
+          <t>8788; 22044</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18735; 35273</t>
+          <t>19551; 35676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26948; 46707</t>
+          <t>27771; 47056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8985; 21348</t>
+          <t>9182; 20637</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4017; 13079</t>
+          <t>3953; 12722</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19518; 36715</t>
+          <t>19984; 37235</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33070; 55711</t>
+          <t>33568; 56348</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17985; 34398</t>
+          <t>18112; 34993</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14645; 30019</t>
+          <t>14501; 30036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42709; 65880</t>
+          <t>41585; 65626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65472; 95484</t>
+          <t>65345; 95924</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,77; 6,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,66</t>
+          <t>0,73; 7,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 14,01</t>
+          <t>0,58; 5,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,97</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,3; 7,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,43</t>
+          <t>0,46; 4,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,41</t>
+          <t>3,02; 13,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,84</t>
+          <t>0,8; 4,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,62</t>
+          <t>0,62; 3,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,45</t>
+          <t>0,97; 4,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,59</t>
+          <t>2,05; 7,6</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,93</t>
+          <t>0,73; 4,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,07</t>
+          <t>0,34; 3,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,94</t>
+          <t>2,86; 7,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,25</t>
+          <t>3,32; 9,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,36</t>
+          <t>0,67; 4,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,38</t>
+          <t>0,9; 5,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,69</t>
+          <t>0,84; 4,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,28</t>
+          <t>3,8; 10,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,28</t>
+          <t>0,87; 3,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,51</t>
+          <t>0,95; 3,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,93</t>
+          <t>2,23; 5,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,19</t>
+          <t>4,13; 8,31</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,87%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5,94%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,97</t>
+          <t>1,25; 7,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 8,71</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,43</t>
+          <t>2,86; 9,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,85</t>
+          <t>2,31; 7,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,75</t>
+          <t>1,39; 8,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>1,56; 8,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 10,3</t>
+          <t>3,36; 9,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,46</t>
+          <t>4,51; 11,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,35</t>
+          <t>2,1; 6,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,65</t>
+          <t>1,23; 5,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,48</t>
+          <t>4,04; 8,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,86</t>
+          <t>3,91; 8,19</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,22</t>
+          <t>0,86; 5,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,96</t>
+          <t>0,87; 5,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 15,35</t>
+          <t>2,21; 8,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,4</t>
+          <t>5,23; 11,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,12</t>
+          <t>0,8; 4,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,03</t>
+          <t>0,64; 5,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,47</t>
+          <t>6,18; 15,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,79</t>
+          <t>2,55; 7,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,94</t>
+          <t>1,26; 4,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,56</t>
+          <t>1,12; 4,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,47</t>
+          <t>4,75; 10,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,82</t>
+          <t>4,39; 8,44</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,42</t>
+          <t>1,76; 4,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,62</t>
+          <t>0,67; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,79</t>
+          <t>3,51; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,06</t>
+          <t>4,49; 7,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,9</t>
+          <t>1,37; 3,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,36</t>
+          <t>1,93; 4,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,52</t>
+          <t>3,68; 6,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,39</t>
+          <t>4,48; 7,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,39</t>
+          <t>1,77; 3,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,96</t>
+          <t>1,52; 3,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,99</t>
+          <t>3,95; 6,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,72</t>
+          <t>4,9; 7,21</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2869</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1275</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3537</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1739</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2869</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4484</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3877</t>
+          <t>683; 6156</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1335; 8248</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>476; 4789</t>
+          <t>716; 6989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1679; 8060</t>
+          <t>293; 2806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>688; 6164</t>
+          <t>0; 4224</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1351; 7916</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>786; 7300</t>
+          <t>470; 4504</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>387; 3940</t>
+          <t>1572; 6962</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1328; 8078</t>
+          <t>1333; 8125</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1338; 7819</t>
+          <t>1341; 8106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1920; 8937</t>
+          <t>1943; 9165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2598; 9023</t>
+          <t>2101; 7802</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10415</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3231</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3631</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3783</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9320</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2651</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10415</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>18280</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1248; 7351</t>
+          <t>1376; 8114</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1323; 8074</t>
+          <t>653; 6552</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1289; 7725</t>
+          <t>6018; 16682</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5402; 14740</t>
+          <t>5230; 14456</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1350; 8237</t>
+          <t>1261; 7712</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>680; 6540</t>
+          <t>1428; 8327</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6007; 16192</t>
+          <t>1314; 7697</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6333; 16945</t>
+          <t>5525; 14732</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3867; 12327</t>
+          <t>3279; 12337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3267; 12360</t>
+          <t>3366; 12299</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8653; 21749</t>
+          <t>8163; 21588</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13765; 27993</t>
+          <t>12529; 25196</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8017</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3344</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4198</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8577</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12098</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3859</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8017</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>22364</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1220; 7754</t>
+          <t>1291; 7491</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1868; 8539</t>
+          <t>0; 4616</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4504; 13604</t>
+          <t>3777; 12993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6922; 18866</t>
+          <t>4633; 15829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1606; 8001</t>
+          <t>1198; 7542</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5069</t>
+          <t>1529; 8484</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4299; 13610</t>
+          <t>4856; 14241</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4714; 15849</t>
+          <t>7924; 20862</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3412; 12044</t>
+          <t>3986; 13088</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2708; 11292</t>
+          <t>2467; 10897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10573; 23456</t>
+          <t>11175; 23537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13989; 30376</t>
+          <t>14683; 30765</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23238</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3150</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2820</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>12190</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10763</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3263</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5787</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22951</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>34519</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1202; 6381</t>
+          <t>1281; 7865</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>734; 6884</t>
+          <t>1152; 7267</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8001; 18744</t>
+          <t>2867; 11382</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6117; 17633</t>
+          <t>15300; 33532</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1283; 7587</t>
+          <t>1215; 6917</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1179; 7939</t>
+          <t>736; 6644</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2838; 11015</t>
+          <t>7544; 18571</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15345; 32955</t>
+          <t>6539; 18608</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3777; 11797</t>
+          <t>3773; 12145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2853; 11266</t>
+          <t>2763; 10792</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12134; 26401</t>
+          <t>11983; 25776</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24337; 45429</t>
+          <t>24090; 46353</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>42328</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36062</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79646</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6303; 17237</t>
+          <t>9318; 21718</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8788; 22044</t>
+          <t>3583; 12897</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19551; 35676</t>
+          <t>20042; 36656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27771; 47056</t>
+          <t>31498; 55840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9182; 20637</t>
+          <t>6875; 17028</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3953; 12722</t>
+          <t>9196; 21670</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19984; 37235</t>
+          <t>19342; 35472</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33568; 56348</t>
+          <t>28185; 48112</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18112; 34993</t>
+          <t>18219; 34190</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14501; 30036</t>
+          <t>15435; 30955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41585; 65626</t>
+          <t>43336; 66358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65345; 95924</t>
+          <t>65216; 95923</t>
         </is>
       </c>
     </row>
